--- a/exports/study_2026-05-12/TMC_NBeltLineRd_NorthwestDr_2026-05-12.xlsx
+++ b/exports/study_2026-05-12/TMC_NBeltLineRd_NorthwestDr_2026-05-12.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12449</v>
+        <v>13645</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4408</v>
+        <v>5033</v>
       </c>
       <c r="C7" t="n">
-        <v>1001</v>
+        <v>824</v>
       </c>
       <c r="D7" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5543</v>
+        <v>5981</v>
       </c>
     </row>
     <row r="8">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5087</v>
+        <v>5921</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5506</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="9">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
         <v>979</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1336</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="10">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>9558</v>
+        <v>11020</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>1354</v>
+        <v>1129</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>1519</v>
+        <v>1478</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>18</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>12449</v>
+        <v>13645</v>
       </c>
     </row>
   </sheetData>
@@ -651,7 +651,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>raw events: 12449</t>
+          <t>raw events: 13645</t>
         </is>
       </c>
     </row>
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4408</v>
+        <v>5033</v>
       </c>
       <c r="C3" t="n">
-        <v>1001</v>
+        <v>824</v>
       </c>
       <c r="D3" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5543</v>
+        <v>5981</v>
       </c>
     </row>
     <row r="4">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5087</v>
+        <v>5921</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5506</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="5">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="D5" t="n">
         <v>979</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1336</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="6">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>535</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4">
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C4" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>588</v>
+        <v>631</v>
       </c>
     </row>
     <row r="5">
@@ -1048,19 +1048,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="C5" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>608</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1142,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>566</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>448</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="C8" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>412</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>424</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="C10" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>445</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11">
@@ -1396,19 +1396,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C11" t="n">
         <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>339</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="C12" t="n">
         <v>18</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>9</v>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>315</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C13" t="n">
         <v>27</v>
@@ -1524,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>348</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14">
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="C14" t="n">
         <v>27</v>
@@ -1582,7 +1582,7 @@
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>373</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C15" t="n">
         <v>39</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>421</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="C16" t="n">
         <v>36</v>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>370</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17">
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>413</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18">
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="C18" t="n">
         <v>31</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>389</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C19" t="n">
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
         <v>58</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>608</v>
+        <v>666</v>
       </c>
     </row>
     <row r="20">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -1930,13 +1930,13 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L20" t="n">
         <v>64</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>557</v>
+        <v>607</v>
       </c>
     </row>
     <row r="21">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="C21" t="n">
         <v>22</v>
@@ -1988,13 +1988,13 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L21" t="n">
         <v>55</v>
@@ -2012,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>676</v>
+        <v>732</v>
       </c>
     </row>
     <row r="22">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C22" t="n">
         <v>39</v>
@@ -2046,13 +2046,13 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L22" t="n">
         <v>68</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>696</v>
+        <v>752</v>
       </c>
     </row>
     <row r="23">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="C23" t="n">
         <v>33</v>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L23" t="n">
         <v>63</v>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>684</v>
+        <v>749</v>
       </c>
     </row>
     <row r="24">
@@ -2150,34 +2150,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="C24" t="n">
         <v>43</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L24" t="n">
         <v>80</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>753</v>
+        <v>809</v>
       </c>
     </row>
     <row r="25">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="C25" t="n">
         <v>36</v>
@@ -2220,13 +2220,13 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>350</v>
+        <v>404</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
         <v>101</v>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>784</v>
+        <v>847</v>
       </c>
     </row>
     <row r="26">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C26" t="n">
         <v>37</v>
@@ -2278,13 +2278,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>350</v>
+        <v>416</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L26" t="n">
         <v>64</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>697</v>
+        <v>773</v>
       </c>
     </row>
     <row r="27">
@@ -2324,34 +2324,34 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>4408</v>
+        <v>5033</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>1001</v>
+        <v>824</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>5</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>5087</v>
+        <v>5921</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>5</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>979</v>
@@ -2360,7 +2360,7 @@
         <v>10</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>7</v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>12449</v>
+        <v>13645</v>
       </c>
     </row>
   </sheetData>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>12449</v>
+        <v>13645</v>
       </c>
     </row>
     <row r="2">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12449</v>
+        <v>13645</v>
       </c>
     </row>
   </sheetData>
